--- a/data/trans_orig/P42C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Habitat-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2012 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71590</t>
+          <t>71478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107013</t>
+          <t>109615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>89220</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>71590</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>107013</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>20,55%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431553</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>411158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413760</t>
+          <t>411158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449183</t>
+          <t>449295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>431553</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>413760</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>449183</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>79,45%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>86,25%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520773</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>520773</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>520773</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>520773</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214834</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189518</t>
+          <t>188148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240607</t>
+          <t>240411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>214834</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>189518</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>240607</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>561729</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>588415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>535956</t>
+          <t>536152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587045</t>
+          <t>588415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>561729</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>535956</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>587045</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>75,6%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>776563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>776563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>776563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>776563</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>776563</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>776563</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160802</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139352</t>
+          <t>138846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185597</t>
+          <t>186231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>160802</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>139352</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>185597</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>435</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476362</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>450933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>498318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451567</t>
+          <t>450933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497812</t>
+          <t>498318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>476362</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>451567</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>497812</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>74,76%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>637164</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>637164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>637164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>637164</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>637164</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>637164</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190820</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166384</t>
+          <t>165527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215484</t>
+          <t>215819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>190820</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>166384</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>215484</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>614715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>640008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590051</t>
+          <t>589716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639151</t>
+          <t>640008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>614715</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>590051</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>639151</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>73,25%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>79,34%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>805535</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>805535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>805535</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>805535</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>805535</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>805535</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>601929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>701351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>611083</t>
+          <t>601929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>705108</t>
+          <t>701351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>655675</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>611083</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>705108</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2084359</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2038683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2138105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2034926</t>
+          <t>2038683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2128951</t>
+          <t>2138105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2084359</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2034926</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2128951</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>74,27%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2524</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2432,14 +1847,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2453,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2472,25 +1886,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +1908,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2510,17 +1917,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2591,41 +1987,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2648,13 +2009,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62905</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,47 +2083,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>48545</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35866</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>62905</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445522</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431162</t>
+          <t>430007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458201</t>
+          <t>457553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,47 +2161,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>445522</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>431162</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>458201</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>87,27%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>491</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494067</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>494067</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>494067</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>494067</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97100</t>
+          <t>98329</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138643</t>
+          <t>138460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,47 +2321,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>117083</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>97100</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>138643</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>726502</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>705125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>745256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>704942</t>
+          <t>705125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>746485</t>
+          <t>745256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,47 +2399,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>726502</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>704942</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>746485</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>843585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>843585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>843585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>843585</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>843585</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>843585</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97428</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116676</t>
+          <t>115551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,47 +2559,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>97428</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>79406</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>116676</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505363</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>523295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>486115</t>
+          <t>487240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523385</t>
+          <t>523295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,47 +2637,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>505363</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>486115</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>523385</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>83,84%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>80,64%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>570</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602791</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>602791</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>602791</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>602791</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3698,37 +2737,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166475</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +2782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>142855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190902</t>
+          <t>189551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,47 +2797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>166475</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>142770</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>190902</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3811,37 +2815,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669836</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>646760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>693456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +2860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>645409</t>
+          <t>646760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693541</t>
+          <t>693456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,47 +2875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>669836</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>645409</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>693541</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>82,93%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -3924,37 +2893,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3988,41 +2957,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>836311</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>836311</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>836311</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4041,37 +2975,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429531</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +3020,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>395628</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472258</t>
+          <t>470981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,47 +3035,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>429531</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>395628</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>472258</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>17,01%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -4154,37 +3053,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2347223</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2305773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2386329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +3098,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2304496</t>
+          <t>2305773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2381126</t>
+          <t>2386329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,47 +3113,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2347223</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2304496</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2381126</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>82,99%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>85,75%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -4267,37 +3131,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4331,41 +3195,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2622</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4379,14 +3208,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4400,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4419,25 +3247,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +3269,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4457,17 +3278,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4538,41 +3348,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4595,13 +3370,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4616,37 +3384,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46941</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +3429,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57971</t>
+          <t>58447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,47 +3444,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>46941</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>37572</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>57971</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -4729,37 +3462,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315699</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +3507,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304669</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325068</t>
+          <t>325676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,47 +3522,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>315699</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>304669</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>325068</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>87,06%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -4842,37 +3540,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362640</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362640</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4906,41 +3604,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>362640</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>362640</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>362640</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4959,37 +3622,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +3667,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100442</t>
+          <t>99789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132070</t>
+          <t>133104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,47 +3682,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>116043</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>100442</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>132070</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -5072,37 +3700,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>433019</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +3745,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416992</t>
+          <t>415958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448620</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,47 +3760,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>433019</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>416992</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>448620</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>75,95%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -5185,37 +3778,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>922</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549062</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549062</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5249,41 +3842,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>549062</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>549062</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>549062</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5302,37 +3860,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +3905,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102577</t>
+          <t>103204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154413</t>
+          <t>153801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,47 +3920,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>133077</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>102577</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>154413</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -5415,37 +3938,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>423</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>296208</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +3983,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274872</t>
+          <t>275484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326708</t>
+          <t>326081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,47 +3998,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>296208</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>274872</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>326708</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5528,37 +4016,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5592,41 +4080,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>429285</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>429285</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>429285</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5645,37 +4098,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171276</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>199195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +4143,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120434</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202002</t>
+          <t>199195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,47 +4158,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>171276</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>120434</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>202002</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4176,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>690</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502542</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +4221,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>471816</t>
+          <t>474623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553384</t>
+          <t>553661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,47 +4236,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>502542</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>471816</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>553384</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>82,13%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -5871,37 +4254,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>952</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673818</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5935,41 +4318,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>673818</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>673818</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>673818</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5988,37 +4336,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467337</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>503641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +4381,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>411727</t>
+          <t>403168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>508802</t>
+          <t>503641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,47 +4396,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>467337</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>411727</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>508802</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4414,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1547468</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1511164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1611637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +4459,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1506003</t>
+          <t>1511164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1603078</t>
+          <t>1611637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,47 +4474,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1547468</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1506003</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1603078</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>74,75%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -6214,37 +4492,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6278,41 +4556,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3179</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6326,14 +4569,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P42C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Habitat-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109615</t>
+          <t>109582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109615</t>
+          <t>109582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411158</t>
+          <t>411191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449295</t>
+          <t>447965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411158</t>
+          <t>411191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449295</t>
+          <t>447965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188148</t>
+          <t>191064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>240411</t>
+          <t>244607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188148</t>
+          <t>191064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240411</t>
+          <t>244607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>536152</t>
+          <t>531956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588415</t>
+          <t>585499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>536152</t>
+          <t>531956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588415</t>
+          <t>585499</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138846</t>
+          <t>140548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186231</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138846</t>
+          <t>140548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186231</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450933</t>
+          <t>453070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498318</t>
+          <t>496616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450933</t>
+          <t>453070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>498318</t>
+          <t>496616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165527</t>
+          <t>168252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215819</t>
+          <t>217254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165527</t>
+          <t>168252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215819</t>
+          <t>217254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589716</t>
+          <t>588281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640008</t>
+          <t>637283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589716</t>
+          <t>588281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640008</t>
+          <t>637283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>601929</t>
+          <t>610767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>701351</t>
+          <t>709432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601929</t>
+          <t>610767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>701351</t>
+          <t>709432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2038683</t>
+          <t>2030602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2138105</t>
+          <t>2129267</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2038683</t>
+          <t>2030602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2138105</t>
+          <t>2129267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>63066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>63066</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430007</t>
+          <t>431001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457553</t>
+          <t>457255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430007</t>
+          <t>431001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457553</t>
+          <t>457255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98329</t>
+          <t>97192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138460</t>
+          <t>137046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98329</t>
+          <t>97192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138460</t>
+          <t>137046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705125</t>
+          <t>706539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>745256</t>
+          <t>746393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705125</t>
+          <t>706539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>745256</t>
+          <t>746393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>79651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115551</t>
+          <t>116388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>79651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115551</t>
+          <t>116388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487240</t>
+          <t>486403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523295</t>
+          <t>523140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>487240</t>
+          <t>486403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523295</t>
+          <t>523140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142855</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189551</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142855</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189551</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>646760</t>
+          <t>644831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>693456</t>
+          <t>693053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>646760</t>
+          <t>644831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693456</t>
+          <t>693053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390425</t>
+          <t>393932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470981</t>
+          <t>471432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390425</t>
+          <t>393932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>470981</t>
+          <t>471432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2305773</t>
+          <t>2305322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2386329</t>
+          <t>2382822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2305773</t>
+          <t>2305322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2386329</t>
+          <t>2382822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -3389,32 +3389,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>49984</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58447</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>49984</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58447</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -3467,32 +3467,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>315699</t>
+          <t>338638</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>326729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325676</t>
+          <t>347912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3502,32 +3502,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>315699</t>
+          <t>338638</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>326729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325676</t>
+          <t>347912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>388622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3627,32 +3627,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>130922</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99789</t>
+          <t>112878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133104</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3662,32 +3662,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>130922</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99789</t>
+          <t>112878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133104</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>433019</t>
+          <t>478297</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415958</t>
+          <t>459548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449273</t>
+          <t>496341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>433019</t>
+          <t>478297</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415958</t>
+          <t>459548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449273</t>
+          <t>496341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -3783,17 +3783,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3818,17 +3818,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>549062</t>
+          <t>609219</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3865,32 +3865,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>147354</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>129332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153801</t>
+          <t>167052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3900,32 +3900,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>147354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>129332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153801</t>
+          <t>167052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -3943,32 +3943,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296208</t>
+          <t>313877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275484</t>
+          <t>294179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>326081</t>
+          <t>331899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3978,32 +3978,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>296208</t>
+          <t>313877</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275484</t>
+          <t>294179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326081</t>
+          <t>331899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -4021,17 +4021,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4103,32 +4103,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>171276</t>
+          <t>184565</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120157</t>
+          <t>165001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199195</t>
+          <t>206037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4138,32 +4138,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>171276</t>
+          <t>184565</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120157</t>
+          <t>165001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199195</t>
+          <t>206037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -4181,32 +4181,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>502542</t>
+          <t>466607</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474623</t>
+          <t>445135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>553661</t>
+          <t>486171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4216,32 +4216,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>502542</t>
+          <t>466607</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474623</t>
+          <t>445135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553661</t>
+          <t>486171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -4259,17 +4259,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4294,17 +4294,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>673818</t>
+          <t>651172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4341,32 +4341,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>403168</t>
+          <t>477218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>503641</t>
+          <t>548651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4376,32 +4376,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>403168</t>
+          <t>477218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>503641</t>
+          <t>548651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -4419,32 +4419,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1547468</t>
+          <t>1597419</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1511164</t>
+          <t>1561592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1611637</t>
+          <t>1633025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4454,32 +4454,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1547468</t>
+          <t>1597419</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1511164</t>
+          <t>1561592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1611637</t>
+          <t>1633025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
